--- a/submission_summary.xlsx
+++ b/submission_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Submitter Name</t>
+          <t>Submitter</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -457,6 +457,11 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Votes</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>League</t>
         </is>
       </c>
     </row>
@@ -487,6 +492,11 @@
       <c r="F2" t="n">
         <v>35</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -515,6 +525,11 @@
       <c r="F3" t="n">
         <v>20</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +558,11 @@
       <c r="F4" t="n">
         <v>6</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,6 +591,11 @@
       <c r="F5" t="n">
         <v>32</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -599,6 +624,11 @@
       <c r="F6" t="n">
         <v>39</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -627,6 +657,11 @@
       <c r="F7" t="n">
         <v>23</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -655,6 +690,11 @@
       <c r="F8" t="n">
         <v>14</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -683,6 +723,11 @@
       <c r="F9" t="n">
         <v>39</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -711,6 +756,11 @@
       <c r="F10" t="n">
         <v>22</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -739,6 +789,11 @@
       <c r="F11" t="n">
         <v>36</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -767,6 +822,11 @@
       <c r="F12" t="n">
         <v>20</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -795,6 +855,11 @@
       <c r="F13" t="n">
         <v>15</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -823,6 +888,11 @@
       <c r="F14" t="n">
         <v>23</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -851,6 +921,11 @@
       <c r="F15" t="n">
         <v>49</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -879,6 +954,11 @@
       <c r="F16" t="n">
         <v>39</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -907,6 +987,11 @@
       <c r="F17" t="n">
         <v>37</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -935,6 +1020,11 @@
       <c r="F18" t="n">
         <v>31</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -963,6 +1053,11 @@
       <c r="F19" t="n">
         <v>9</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -991,6 +1086,11 @@
       <c r="F20" t="n">
         <v>48</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1019,6 +1119,11 @@
       <c r="F21" t="n">
         <v>33</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1047,6 +1152,11 @@
       <c r="F22" t="n">
         <v>24</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1075,6 +1185,11 @@
       <c r="F23" t="n">
         <v>10</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1103,6 +1218,11 @@
       <c r="F24" t="n">
         <v>30</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1131,6 +1251,11 @@
       <c r="F25" t="n">
         <v>37</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1159,6 +1284,11 @@
       <c r="F26" t="n">
         <v>40</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1187,6 +1317,11 @@
       <c r="F27" t="n">
         <v>31</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1215,6 +1350,11 @@
       <c r="F28" t="n">
         <v>34</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1243,6 +1383,11 @@
       <c r="F29" t="n">
         <v>37</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1271,6 +1416,11 @@
       <c r="F30" t="n">
         <v>20</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1299,6 +1449,11 @@
       <c r="F31" t="n">
         <v>18</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1327,6 +1482,11 @@
       <c r="F32" t="n">
         <v>35</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1355,6 +1515,11 @@
       <c r="F33" t="n">
         <v>23</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1383,6 +1548,11 @@
       <c r="F34" t="n">
         <v>35</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1411,6 +1581,11 @@
       <c r="F35" t="n">
         <v>46</v>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1439,6 +1614,11 @@
       <c r="F36" t="n">
         <v>32</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1467,6 +1647,11 @@
       <c r="F37" t="n">
         <v>34</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1495,6 +1680,11 @@
       <c r="F38" t="n">
         <v>29</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1523,6 +1713,11 @@
       <c r="F39" t="n">
         <v>16</v>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1551,6 +1746,11 @@
       <c r="F40" t="n">
         <v>12</v>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1579,6 +1779,11 @@
       <c r="F41" t="n">
         <v>36</v>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1607,6 +1812,11 @@
       <c r="F42" t="n">
         <v>27</v>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1635,6 +1845,11 @@
       <c r="F43" t="n">
         <v>30</v>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1663,6 +1878,11 @@
       <c r="F44" t="n">
         <v>29</v>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1691,6 +1911,11 @@
       <c r="F45" t="n">
         <v>38</v>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1719,6 +1944,11 @@
       <c r="F46" t="n">
         <v>27</v>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1747,6 +1977,11 @@
       <c r="F47" t="n">
         <v>41</v>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1775,6 +2010,11 @@
       <c r="F48" t="n">
         <v>17</v>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1803,6 +2043,11 @@
       <c r="F49" t="n">
         <v>43</v>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1831,6 +2076,11 @@
       <c r="F50" t="n">
         <v>41</v>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1859,6 +2109,11 @@
       <c r="F51" t="n">
         <v>3</v>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1887,6 +2142,11 @@
       <c r="F52" t="n">
         <v>25</v>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1915,6 +2175,11 @@
       <c r="F53" t="n">
         <v>42</v>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1943,6 +2208,11 @@
       <c r="F54" t="n">
         <v>35</v>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1971,6 +2241,11 @@
       <c r="F55" t="n">
         <v>16</v>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1999,6 +2274,11 @@
       <c r="F56" t="n">
         <v>27</v>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2027,6 +2307,11 @@
       <c r="F57" t="n">
         <v>6</v>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2055,6 +2340,11 @@
       <c r="F58" t="n">
         <v>22</v>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2083,6 +2373,11 @@
       <c r="F59" t="n">
         <v>35</v>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2111,6 +2406,11 @@
       <c r="F60" t="n">
         <v>45</v>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2139,6 +2439,11 @@
       <c r="F61" t="n">
         <v>44</v>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2167,6 +2472,11 @@
       <c r="F62" t="n">
         <v>48</v>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2195,6 +2505,11 @@
       <c r="F63" t="n">
         <v>9</v>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2223,6 +2538,11 @@
       <c r="F64" t="n">
         <v>37</v>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2251,6 +2571,11 @@
       <c r="F65" t="n">
         <v>44</v>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2279,6 +2604,11 @@
       <c r="F66" t="n">
         <v>14</v>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2307,6 +2637,11 @@
       <c r="F67" t="n">
         <v>16</v>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2335,6 +2670,11 @@
       <c r="F68" t="n">
         <v>32</v>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2363,6 +2703,11 @@
       <c r="F69" t="n">
         <v>38</v>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2391,6 +2736,11 @@
       <c r="F70" t="n">
         <v>38</v>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2419,6 +2769,11 @@
       <c r="F71" t="n">
         <v>34</v>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2447,6 +2802,11 @@
       <c r="F72" t="n">
         <v>26</v>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2475,6 +2835,11 @@
       <c r="F73" t="n">
         <v>35</v>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2503,6 +2868,11 @@
       <c r="F74" t="n">
         <v>20</v>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2531,6 +2901,11 @@
       <c r="F75" t="n">
         <v>51</v>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2559,6 +2934,11 @@
       <c r="F76" t="n">
         <v>35</v>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2587,6 +2967,11 @@
       <c r="F77" t="n">
         <v>43</v>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2615,6 +3000,11 @@
       <c r="F78" t="n">
         <v>-16</v>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2643,6 +3033,11 @@
       <c r="F79" t="n">
         <v>36</v>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2671,6 +3066,11 @@
       <c r="F80" t="n">
         <v>48</v>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2699,6 +3099,11 @@
       <c r="F81" t="n">
         <v>43</v>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2727,6 +3132,11 @@
       <c r="F82" t="n">
         <v>30</v>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2755,6 +3165,11 @@
       <c r="F83" t="n">
         <v>39</v>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2783,6 +3198,11 @@
       <c r="F84" t="n">
         <v>34</v>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2811,6 +3231,11 @@
       <c r="F85" t="n">
         <v>-1</v>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2838,6 +3263,11 @@
       </c>
       <c r="F86" t="n">
         <v>15</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/submission_summary.xlsx
+++ b/submission_summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Artist(s)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Submitter</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Round Order</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Round Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Votes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>League</t>
         </is>

--- a/submission_summary.xlsx
+++ b/submission_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3258,6 +3258,567 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Van Halen</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Panama - 2015 Remaster</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Jen Langley</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>6</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>35</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Limelight</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>26</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cardiacs</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Is This The Life?</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>6</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>43</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Porcupine Tree</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Shesmovedon</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Michael Barry</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>20</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Mdou Moctar</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Afrique Victime</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>45</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Suede</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>The Asphalt World (Remastered)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>10</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>The Darkness</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>I Believe in a Thing Called Love - Single Version</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>6</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>12</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Steve Reich, Pat Metheny</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Electric Counterpoint: III. Fast</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>18</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Jackson Browne</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Late for the Sky - Remastered</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>6</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>34</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Built To Spill</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Carry the Zero</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>6</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>45</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Black Mountain</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Space to Bakersfield</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>6</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>40</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tears For Fears</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Everybody Wants To Rule The World</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>6</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>14</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sleater-Kinney</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Let's Call It Love</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>6</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>22</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Jeff Beck</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Beck's Bolero - Instrumental</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>6</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>21</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Bettie Serveert</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Leg</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>6</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>10</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Dinosaur Jr.</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Freak Scene</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>6</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>57</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Marquee Moon</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Guitar Lover</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>58</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/submission_summary.xlsx
+++ b/submission_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3819,6 +3819,534 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Four Tops</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Bernadette</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>31</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Badfinger</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>No Matter What - Remastered 2010</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>7</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>34</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>22-Pistepirkko</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Birdy</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>7</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>35</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Kenny Rogers &amp; The First Edition</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Just Dropped In (To See What Condition My Condition Is In)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Jen Langley</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>7</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>29</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Jonathan Richman, The Modern Lovers</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ice Cream Man (Live)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>7</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>38</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Seven and Seven Is</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>7</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>18</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Midnight Oil</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Read About It - Live</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>7</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>36</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Raspberries</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Overnight Sensation</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>7</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>39</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Hoodoo Gurus</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Tojo - Remaster 2005</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>7</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>35</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Small Crimes</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Michael Barry</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>7</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>13</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Roxy Music</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>In Every Dream Home A Heartache</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>7</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>43</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Matthew Sweet</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Sick of Myself</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>7</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>34</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>NOFX</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Please Play This Song On The Radio</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>7</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>10</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Leon Bridges</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Bad Bad News</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>7</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>35</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>UNKLE, Badly Drawn Boy</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Nursery Rhyme / Breather</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>7</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>20</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>The Stooges</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>T.V. Eye</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>7</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Keep Me Around</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>30</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/submission_summary.xlsx
+++ b/submission_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4347,6 +4347,534 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Ultravox</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>I Want To Be A Machine</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>22</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>The Twilight Sad</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>I Became a Prostitute</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>8</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>45</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Flip Top Head</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>I Can't Wait Until I'm Old</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>46</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>The Murder City Devils</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>I Want A Lot Now (So Come On)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>26</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>The Pogues</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>I'm a Man You Don't Meet Every Day</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Jen Langley</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>11</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Owen Pallett</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>I Am Not Afraid</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>8</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>30</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Melody's Echo Chamber</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>I Follow You</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>8</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>25</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Claus Hempler</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Jeg Drømmer Om En Sang</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>35</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Mannequin Pussy</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>I Got Heaven</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>8</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>50</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jimmie Spheeris</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>I Am the Mercury</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>31</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Foo Fighters</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>I'll Stick Around</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Michael Barry</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ted Leo and the Pharmacists, The Pharmacists</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Me and Mia</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>24</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Anna Waronker</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>I Wish You Well</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>18</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Iguana Death Cult</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>I Like It, It's Nice</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>21</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Brigitte Calls Me Baby</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>I Danced with Another Love in My Dream</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>8</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>10</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>The Horrors</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>I Can See Through You</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>8</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>I’ll Be Gone</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>29</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/submission_summary.xlsx
+++ b/submission_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,7 +928,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>Excruciating Musical Suicide Bombing</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>Excruciating Musical Suicide Bombing</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>Excruciating Musical Suicide Bombing</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>Excruciating Musical Suicide Bombing</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>Excruciating Musical Suicide Bombing</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>Excruciating Musical Suicide Bombing</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>Excruciating Musical Suicide Bombing</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>Excruciating Musical Suicide Bombing</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4870,6 +4870,1062 @@
         <v>29</v>
       </c>
       <c r="G135" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>The Frogs</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Fuck Off</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>9</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>38</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Jason Isbell</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Speed Trap Town</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Jen Langley</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>9</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>23</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Bob Dylan</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Time Passes Slowly</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>9</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>20</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>GAYLE</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>abcdefu (angrier)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>9</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>8</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Yorkston/Thorne/Khan</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Little Black Buzzer</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>9</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>23</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Klangstof</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Island</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>9</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>40</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Dismemberment Plan</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>The Ice Of Boston</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>9</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>32</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>The Cramps</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>People Ain't No Good</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>9</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>27</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>The Human League</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Life On Your Own</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>9</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>34</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Jenn Champion</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>No One - Piano Version</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>9</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>27</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Calexico</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Spokes</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>9</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>29</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Kenny Drew, Niels-Henning Ørsted Pedersen</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>I skovens dybe stille ro</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>9</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>23</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sebadoh</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Not Too Amused - Remastered</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>9</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>46</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Red City Radio</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>In the Meantime...</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>9</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>19</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>The Menzingers</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Irish Goodbyes</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>9</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>18</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Catherine Wheel</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Crank</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Excruciating Musical Suicide Bombing</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>9</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Go Away</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>43</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Crosby, Stills, Nash &amp; Young</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>42</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Lyla June</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>All Nations Rise</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>40</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Don McLean</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>American Pie</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>11</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Gil Scott-Heron</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Whitey on the Moon</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>51</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Siouxsie and the Banshees</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Cities In Dust</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>45</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Jesus Jones</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Right Here Right Now</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>4</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Redskins</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Kick Over the Statues!</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>28</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Warren Zevon</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>19</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Gordon Lightfoot</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>The Wreck of the Edmund Fitzgerald</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>3</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Steve Earle</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Christmas in Washington</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>40</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Andrew Bird</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Lusitania</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>44</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Styx</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Suite Madame Blue - Live In New Orleans/1983</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Excruciating Musical Suicide Bombing</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sons of Southern Ulster</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Billyhill Hall</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>48</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>The Boomtown Rats</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>I Don't Like Mondays</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Jen Langley</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>24</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Billy Bragg</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>The World Turned Upside Down</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>38</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Firefly 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Orchestral Manoeuvres In The Dark</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>88 Seconds in Greensboro - Remastered 2025</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>The Global Sweep of Human History</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>43</v>
+      </c>
+      <c r="G167" t="inlineStr">
         <is>
           <t>Firefly 7</t>
         </is>

--- a/submission_summary.xlsx
+++ b/submission_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,6 +1113,2481 @@
         <v>34</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Myster Ezin</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>The Whitlams</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Gough</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bobby Taylor &amp; The Vancouvers</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Malinda</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>The Murder Capital</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ethel</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Samantha Crain</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kathleen</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Brand New</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Luca - Reprisal Version</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>The Clouds</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hieronymus</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>alt-J</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Matilda</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Boney M.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sunny</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>The Turtles</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Elenore</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lee Potter</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Fleetwood Mac</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sara - 2015 Remaster</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Fruit Bats, Vetiver</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Maureen - Live at Spacebomb Studios</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A Perfect Circle</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Judith</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Excruciating Musical Suicide Bombing</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Men I Trust</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Aaron Neville</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hercules</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A Certain Ratio</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lucinda (EM)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Arlo Parks</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>De Eneste To</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Morten</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>The Veils</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Not Yet</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Lee Potter</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Martha Wainwright</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Bloody Mother Fucking Asshole</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Baxter Dury</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hearty Har</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Can't Keep Waiting</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Family Stereo</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fault Lines</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hector Zazou, Melanie Gabriel</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mmmh</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jeff Buckley</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>If You Knew</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kim Wilde</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kids In America</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Myrkur</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Måneblôt</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Neneh Cherry</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Move With Me</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Excruciating Musical Suicide Bombing</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Seraphina Simone</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sean Ono Lennon</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dead Meat</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pieta Brown</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Dreamin' Of</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Charlotte Gainsbourg</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>The Songs That We Sing</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Miley Cyrus</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Party In The U.S.A.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>The Like</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>I Can See It In Your Eyes</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Rufus Wainwright</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Foolish Love</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Justin Townes Earle</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Harlem River Blues</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Carl Philipp Emanuel Bach, Michael Rische, Kammersymphonie Leipzig</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>II. Andantino</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>The Horne Section</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Granddaddy</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Lynks</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kick the Ball!!</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chef, Isaac Hayes</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chocolate Salty Balls (P.S. I Love You)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sheb Wooley</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>The Purple People Eater</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>They Might Be Giants</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>I Am A Grocery Bag</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ninja Sex Party</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>I Own a Car</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Lucille Bogan</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Shave 'Em Dry II</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Lee Potter</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jake Thackray</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Bantam Cock</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Skee-Lo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>I Wish</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Robyn Hitchcock</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Uncorrected Personality Traits</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>The Refreshments</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Banditos</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Junior Brother</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>This Is My Body</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Frank Zappa, The Mothers</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>King Missile</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sensitive Artist</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Aidan Moffat</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>The Ball of Kirriemuir</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Flight of the Conchords, Jemaine Clement, Bret McKenzie</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Inner City Pressure</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tom Petty</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Girl on LSD - Alternate Version</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Excruciating Musical Suicide Bombing</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Lard</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>70's Rock Must Die</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Faye Richmonde</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tony's Got Hot Nuts</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Lost My Humor</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Voka Gentle</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kinema</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Two Gallants</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Linger On</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>King Crimson</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Starless - Abridged</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Excruciating Musical Suicide Bombing</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>My Brightest Diamond</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Safe House</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Scott Matthews</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Elusive</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Big Star</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Holocaust</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Lee Potter</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Brian Eno</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Always Returning - Remastered 2005</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Tulliah</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Look Away</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>(That's How You Sing) Amazing Grace</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Larmousse</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>A Universal Hello</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Codeine</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Loss Leader</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>S.G. Goodman</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Red Bird Morning</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Babehoven</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Chariot</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Tape</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Beams</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Stan Getz</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Crystal Silence - Previously Unissued</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Galaxie 500</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Listen, The Snow Is Falling</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Eddi Reader</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>My Old Friend the Blues</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Phosphorescent</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Song for Zula</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Hope Sandoval &amp; The Warm Inventions</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Lose Me On the Way</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
